--- a/Test_Cases_Execution 2.xlsx
+++ b/Test_Cases_Execution 2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580" tabRatio="500"/>
+    <workbookView windowWidth="14730" windowHeight="12600" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -591,7 +591,7 @@
     <t>As expected: returned to the calendar; no booking created and data not saved.</t>
   </si>
   <si>
-    <t>TC-034</t>
+    <t>TC-022</t>
   </si>
   <si>
     <t>Search with check-out before check-in</t>
@@ -612,7 +612,7 @@
     <t>Leads into TC-035 and TC-036</t>
   </si>
   <si>
-    <t>TC-035</t>
+    <t>TC-023</t>
   </si>
   <si>
     <t>No negative price for reversed dates</t>
@@ -633,7 +633,7 @@
     <t>Also seen as Total £-160 (run 13268)</t>
   </si>
   <si>
-    <t>TC-037</t>
+    <t>TC-024</t>
   </si>
   <si>
     <t>Booking calendar opens on the chosen month</t>
@@ -654,7 +654,7 @@
     <t>https://drive.google.com/file/d/1CgNKMPlJSgbeQlWxdH6_76NivSjDzQb3/view?usp=sharing</t>
   </si>
   <si>
-    <t>TC-038</t>
+    <t>TC-025</t>
   </si>
   <si>
     <t>Confirmation shows reference and total</t>
@@ -675,7 +675,7 @@
     <t>Total (£340) was shown a moment before, then gone</t>
   </si>
   <si>
-    <t>TC-039</t>
+    <t>TC-026</t>
   </si>
   <si>
     <t>Booked room no longer offered for same dates</t>
@@ -699,7 +699,7 @@
     <t>ID corrected (typo)</t>
   </si>
   <si>
-    <t>TC-040</t>
+    <t>TC-027</t>
   </si>
   <si>
     <t>Fully booked dates show a clear "no rooms" message</t>
@@ -729,7 +729,7 @@
     <t>BLOCKED: add retry plan or leave as an environment limitation</t>
   </si>
   <si>
-    <t>TC-041</t>
+    <t>TC-028</t>
   </si>
   <si>
     <t>Multi-night total price</t>
@@ -747,10 +747,7 @@
     <t>£150 × 2 = £300 + £25 + £15 = £340</t>
   </si>
   <si>
-    <t>Runs 13268, 13269, 13273</t>
-  </si>
-  <si>
-    <t>TC-058</t>
+    <t>TC-029</t>
   </si>
   <si>
     <t>First name trims leading and trailing spaces</t>
@@ -774,7 +771,7 @@
     <t>Add evidence (screenshot); Renumbered (was a duplicate TC-011)</t>
   </si>
   <si>
-    <t>TC-059</t>
+    <t>TC-030</t>
   </si>
   <si>
     <t>Last name trims leading and trailing spaces</t>
@@ -792,7 +789,7 @@
     <t>Add evidence (screenshot); Renumbered (was a duplicate TC-012)</t>
   </si>
   <si>
-    <t>TC-060</t>
+    <t>TC-031</t>
   </si>
   <si>
     <t>Room cards show correct information</t>
@@ -816,7 +813,7 @@
     <t>New case: not yet executed</t>
   </si>
   <si>
-    <t>TC-061</t>
+    <t>TC-032</t>
   </si>
   <si>
     <t>Valid availability search</t>
@@ -836,7 +833,10 @@
     <t xml:space="preserve">becouse there is many pepole are working in the website </t>
   </si>
   <si>
-    <t>TC-022</t>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>TC-034</t>
   </si>
   <si>
     <t>Contact</t>
@@ -861,7 +861,7 @@
     <t>https://drive.google.com/file/d/1vDUxShXRsPlthScgjFtkVYgWZ3-YTOBf/view?usp=sharing</t>
   </si>
   <si>
-    <t>TC-023</t>
+    <t>TC-035</t>
   </si>
   <si>
     <t>Empty contact form</t>
@@ -879,7 +879,7 @@
     <t>https://drive.google.com/file/d/1E81aPkzNVs6rdQ2fpOjlXlFAYSkzMNfJ/view?usp=sharing</t>
   </si>
   <si>
-    <t>TC-024</t>
+    <t>TC-036</t>
   </si>
   <si>
     <t>Subject and message length limits</t>
@@ -901,100 +901,100 @@
     <t>Confirm real limits from the messages shown.</t>
   </si>
   <si>
+    <t>TC-037</t>
+  </si>
+  <si>
+    <t>Double-click Submit sends one message</t>
+  </si>
+  <si>
+    <t>1. Fill contact form validly 2. Double-click Submit 3. Check owner Messages</t>
+  </si>
+  <si>
+    <t>One message arrives</t>
+  </si>
+  <si>
+    <t>Two identical messages; unread count goes up by 2</t>
+  </si>
+  <si>
+    <t>Status conflicts with Actual (two messages sent but marked PASS)</t>
+  </si>
+  <si>
+    <t>TC-038</t>
+  </si>
+  <si>
+    <t>Phone with letters on contact form</t>
+  </si>
+  <si>
+    <t>1. Enter a letters-only phone 2. Submit</t>
+  </si>
+  <si>
+    <t>Phone = abcdefghijk</t>
+  </si>
+  <si>
+    <t>Rejected with a clear message</t>
+  </si>
+  <si>
+    <t>Accepted; owner sees "Phone: abcdefghijk"</t>
+  </si>
+  <si>
+    <t>TC-039</t>
+  </si>
+  <si>
+    <t>Invalid email on contact form</t>
+  </si>
+  <si>
+    <t>1. Enter a badly formatted email 2. Submit</t>
+  </si>
+  <si>
+    <t>Malformed email</t>
+  </si>
+  <si>
+    <t>Rejected; typed data kept</t>
+  </si>
+  <si>
+    <t>Rejected and typed data kept</t>
+  </si>
+  <si>
+    <t>Runs did not list which formats were tried</t>
+  </si>
+  <si>
+    <t>TC-040</t>
+  </si>
+  <si>
+    <t>Owner reads a message</t>
+  </si>
+  <si>
+    <t>1. Send one enquiry 2. Owner opens it 3. Reload</t>
+  </si>
+  <si>
+    <t>One enquiry</t>
+  </si>
+  <si>
+    <t>Marked read; unread count drops; stays read after reload</t>
+  </si>
+  <si>
+    <t>Unread 3 → 2, still read after reload</t>
+  </si>
+  <si>
+    <t>TC-041</t>
+  </si>
+  <si>
+    <t>Phone shown in full to owner</t>
+  </si>
+  <si>
+    <t>1. Send enquiry with a valid phone 2. Owner opens it</t>
+  </si>
+  <si>
+    <t>Valid phone</t>
+  </si>
+  <si>
+    <t>Full, correct number shown</t>
+  </si>
+  <si>
+    <t>Phone number intact</t>
+  </si>
+  <si>
     <t>TC-042</t>
-  </si>
-  <si>
-    <t>Double-click Submit sends one message</t>
-  </si>
-  <si>
-    <t>1. Fill contact form validly 2. Double-click Submit 3. Check owner Messages</t>
-  </si>
-  <si>
-    <t>One message arrives</t>
-  </si>
-  <si>
-    <t>Two identical messages; unread count goes up by 2</t>
-  </si>
-  <si>
-    <t>Status conflicts with Actual (two messages sent but marked PASS)</t>
-  </si>
-  <si>
-    <t>TC-043</t>
-  </si>
-  <si>
-    <t>Phone with letters on contact form</t>
-  </si>
-  <si>
-    <t>1. Enter a letters-only phone 2. Submit</t>
-  </si>
-  <si>
-    <t>Phone = abcdefghijk</t>
-  </si>
-  <si>
-    <t>Rejected with a clear message</t>
-  </si>
-  <si>
-    <t>Accepted; owner sees "Phone: abcdefghijk"</t>
-  </si>
-  <si>
-    <t>TC-044</t>
-  </si>
-  <si>
-    <t>Invalid email on contact form</t>
-  </si>
-  <si>
-    <t>1. Enter a badly formatted email 2. Submit</t>
-  </si>
-  <si>
-    <t>Malformed email</t>
-  </si>
-  <si>
-    <t>Rejected; typed data kept</t>
-  </si>
-  <si>
-    <t>Rejected and typed data kept</t>
-  </si>
-  <si>
-    <t>Runs did not list which formats were tried</t>
-  </si>
-  <si>
-    <t>TC-045</t>
-  </si>
-  <si>
-    <t>Owner reads a message</t>
-  </si>
-  <si>
-    <t>1. Send one enquiry 2. Owner opens it 3. Reload</t>
-  </si>
-  <si>
-    <t>One enquiry</t>
-  </si>
-  <si>
-    <t>Marked read; unread count drops; stays read after reload</t>
-  </si>
-  <si>
-    <t>Unread 3 → 2, still read after reload</t>
-  </si>
-  <si>
-    <t>TC-046</t>
-  </si>
-  <si>
-    <t>Phone shown in full to owner</t>
-  </si>
-  <si>
-    <t>1. Send enquiry with a valid phone 2. Owner opens it</t>
-  </si>
-  <si>
-    <t>Valid phone</t>
-  </si>
-  <si>
-    <t>Full, correct number shown</t>
-  </si>
-  <si>
-    <t>Phone number intact</t>
-  </si>
-  <si>
-    <t>TC-025</t>
   </si>
   <si>
     <t>Admin</t>
@@ -1020,7 +1020,7 @@
     <t>Credentials are taken from the project README; do not commit them to the repo.</t>
   </si>
   <si>
-    <t>TC-026</t>
+    <t>TC-043</t>
   </si>
   <si>
     <t>Admin login with invalid credentials</t>
@@ -1038,7 +1038,7 @@
     <t>As expected: login was rejected for every invalid combination.</t>
   </si>
   <si>
-    <t>TC-027</t>
+    <t>TC-044</t>
   </si>
   <si>
     <t>Booking appears in admin panel</t>
@@ -1057,7 +1057,7 @@
     <t>As expected: the booking was listed with the correct details.</t>
   </si>
   <si>
-    <t>TC-028</t>
+    <t>TC-045</t>
   </si>
   <si>
     <t>Contact message appears in admin</t>
@@ -1075,7 +1075,7 @@
     <t>As expected: the message appeared with its full details.</t>
   </si>
   <si>
-    <t>TC-029</t>
+    <t>TC-046</t>
   </si>
   <si>
     <t>Add and delete a room</t>
@@ -1096,7 +1096,7 @@
     <t>As expected: the room appeared, then was removed from the admin and public pages.</t>
   </si>
   <si>
-    <t>TC-030</t>
+    <t>TC-047</t>
   </si>
   <si>
     <t>Logout and access after logout</t>
@@ -1118,7 +1118,7 @@
     <t>Restored from the original plan (was missing from the sheet).</t>
   </si>
   <si>
-    <t>TC-047</t>
+    <t>TC-048</t>
   </si>
   <si>
     <t>Double-click Create adds one room</t>
@@ -1136,7 +1136,7 @@
     <t>Two identical rooms "912 Single false 120"</t>
   </si>
   <si>
-    <t>TC-048</t>
+    <t>TC-049</t>
   </si>
   <si>
     <t>Duplicate room number rejected</t>
@@ -1154,7 +1154,7 @@
     <t>Seen through the double-click; a separate second create was not recorded</t>
   </si>
   <si>
-    <t>TC-049</t>
+    <t>TC-050</t>
   </si>
   <si>
     <t>Missing room fields are named</t>
@@ -1175,7 +1175,7 @@
     <t>Editing shows "Failed to update room"</t>
   </si>
   <si>
-    <t>TC-050</t>
+    <t>TC-051</t>
   </si>
   <si>
     <t>New price reaches guests</t>
@@ -1196,7 +1196,7 @@
     <t>Price restored afterwards</t>
   </si>
   <si>
-    <t>TC-051</t>
+    <t>TC-052</t>
   </si>
   <si>
     <t>Save Branding without changes</t>
@@ -1244,7 +1244,7 @@
     <t>Opening "+N more" not recorded separately</t>
   </si>
   <si>
-    <t>TC-062</t>
+    <t>TC-054</t>
   </si>
   <si>
     <t>Admin pages without logging in</t>
@@ -1263,7 +1263,7 @@
     <t>Added to close a coverage gap (access control).</t>
   </si>
   <si>
-    <t>TC-063</t>
+    <t>TC-055</t>
   </si>
   <si>
     <t>Edit an existing room</t>
@@ -1283,7 +1283,7 @@
     <t>Added to close a coverage gap (room update).</t>
   </si>
   <si>
-    <t>TC-055</t>
+    <t>TC-056</t>
   </si>
   <si>
     <t>Navigation</t>
@@ -1298,7 +1298,7 @@
     <t>Goes to the Amenities section</t>
   </si>
   <si>
-    <t>TC-056</t>
+    <t>TC-057</t>
   </si>
   <si>
     <t>Footer Quick Links</t>
@@ -1319,7 +1319,7 @@
     <t>Same links in the top menu work</t>
   </si>
   <si>
-    <t>TC-057</t>
+    <t>TC-058</t>
   </si>
   <si>
     <t>Cookie and Privacy pages</t>
@@ -1340,7 +1340,7 @@
     <t>Status conflicts with Actual (not tested but marked PASS)</t>
   </si>
   <si>
-    <t>TC-031</t>
+    <t>TC-059</t>
   </si>
   <si>
     <t>Exploratory</t>
@@ -1362,7 +1362,7 @@
     <t>As expected: the input was not executed and was displayed safely.</t>
   </si>
   <si>
-    <t>TC-032</t>
+    <t>TC-060</t>
   </si>
   <si>
     <t>Responsive layout</t>
@@ -1381,7 +1381,7 @@
     <t>As expected: the layout was usable and the booking flow worked on mobile and tablet widths.</t>
   </si>
   <si>
-    <t>TC-033</t>
+    <t>TC-061</t>
   </si>
   <si>
     <t>Refresh during form filling</t>
@@ -4139,39 +4139,37 @@
       <c r="J29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="11" t="s">
-        <v>227</v>
-      </c>
+      <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
     </row>
     <row r="30" ht="34.5" customHeight="1" spans="1:13">
       <c r="A30" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>69</v>
       </c>
       <c r="F30" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="H30" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="I30" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>234</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>119</v>
@@ -4179,36 +4177,36 @@
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
       <c r="M30" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" ht="34.5" customHeight="1" spans="1:13">
       <c r="A31" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>69</v>
       </c>
       <c r="F31" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G31" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="H31" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>240</v>
-      </c>
       <c r="I31" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J31" s="10" t="s">
         <v>119</v>
@@ -4216,18 +4214,18 @@
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" ht="57" customHeight="1" spans="1:13">
       <c r="A32" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>16</v>
@@ -4236,13 +4234,13 @@
         <v>69</v>
       </c>
       <c r="F32" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="H32" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="I32" s="11"/>
       <c r="J32" s="10" t="s">
@@ -4250,21 +4248,21 @@
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="M32" s="13" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="33" ht="45.75" customHeight="1" spans="1:13">
       <c r="A33" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>16</v>
@@ -4273,13 +4271,13 @@
         <v>17</v>
       </c>
       <c r="F33" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G33" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="H33" s="11" t="s">
         <v>252</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>253</v>
       </c>
       <c r="I33" s="11"/>
       <c r="J33" s="10" t="s">
@@ -4287,14 +4285,16 @@
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" ht="45.75" customHeight="1" spans="1:13">
+      <c r="A34" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="M33" s="13" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="34" ht="45.75" customHeight="1" spans="1:13">
-      <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
       <c r="D34" s="10"/>
@@ -4829,7 +4829,7 @@
         <v>345</v>
       </c>
       <c r="M48" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" ht="23.25" customHeight="1" spans="1:13">
@@ -5090,7 +5090,7 @@
         <v>393</v>
       </c>
       <c r="M55" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" ht="34.5" customHeight="1" spans="1:13">
@@ -5127,7 +5127,7 @@
         <v>399</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:13">
@@ -5397,7 +5397,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="J34 J55 I56 J56 J2:J24 J25:J33 J35:J54 J57:J200">
+    <dataValidation type="list" sqref="I56:J56 J2:J55 J57:J200">
       <formula1>"PASS,FAIL,BLOCKED,NOT RUN"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5715,7 +5715,7 @@
     </row>
     <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B23" s="5">
         <f>COUNTIF('Test Cases'!$D$2:$D$200,A23)</f>
@@ -5803,7 +5803,7 @@
         <v>459</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>242</v>
+        <v>426</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>460</v>
@@ -5951,7 +5951,7 @@
         <v>490</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>491</v>
